--- a/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/StructureDefinition-at-scheduling-appointment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-appointment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:33:33+00:00</t>
+    <t>2026-08-18T09:10:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,7 +463,7 @@
     <t>postponementReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-postponementReason}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-postponementReason}
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <t>cancellationPolicy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
 </t>
   </si>
   <si>
@@ -736,7 +736,7 @@
     <t>Appointment.serviceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
+    <t xml:space="preserve">CodeableReference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -881,7 +881,7 @@
     <t>Appointment.replaces</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-appointment)
 </t>
   </si>
   <si>
@@ -1073,7 +1073,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-slot)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-slot)
 </t>
   </si>
   <si>
@@ -1281,7 +1281,7 @@
     <t>virtualService</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/virtual-service-detail}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/virtual-service-detail}
 </t>
   </si>
   <si>
@@ -2383,7 +2383,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
